--- a/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
@@ -2160,7 +2160,7 @@
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>The Approval Queue is EMPTY by default — none of the 5 seeded orders are in "Submitted for Approval" status. To populate it: run the New Postpaid Activation, New Fixed Line, or New FWA wizard (Sales workspace) and tick the "B2B2C order" checkbox on the contact step — all three wizards now write an order-type string that matches an approval-matrix category (New Postpaid Activation / New Fixed Line Activation / New FWA Postpaid Outdoor Order), so the role gate applies to all of them. Note the two seeded historical orders ORD-90003/ORD-90004 use slightly different order-type strings ("New FWA 5G Outdoor Activation" / "New Fixed Line - Triple Play") than the matrix — that is harmless since both are already Complete/Open and never re-enter the approval flow, but do not use those exact strings as a template if you are hand-editing an order into "Submitted for Approval" for testing; use the wizard-created strings shown in the matrix below instead. MNP Postpaid Port-In cannot currently be reached via the live MNP wizard (it always creates orderType "Activation" with status "Pending", never "Submitted for Approval") — that matrix entry only matches if you hand-edit an order to orderType "MNP Postpaid Port-In" + status "Submitted for Approval". Also: CUST-1002 (HRN) will trigger the advance-payment gate on the New Postpaid wizard, which independently sets the order to Submitted for Approval regardless of the B2B2C checkbox.</t>
+          <t>The Approval Queue is EMPTY by default — none of the 5 seeded orders are in "Submitted for Approval" status. To populate it: run the New Postpaid Activation, New Fixed Line, New FWA, or MNP Port-In wizard (Sales workspace) and tick the "B2B2C order" checkbox on the contact step — all four wizards now write an order-type string that matches an approval-matrix category (New Postpaid Activation / New Fixed Line Activation / New FWA Postpaid Outdoor Order / MNP Postpaid Port-In), so the role gate applies to all of them. Note the two seeded historical orders ORD-90003/ORD-90004 use slightly different order-type strings ("New FWA 5G Outdoor Activation" / "New Fixed Line - Triple Play") than the matrix — that is harmless since both are already Complete/Open and never re-enter the approval flow, but do not use those exact strings as a template if you are hand-editing an order into "Submitted for Approval" for testing; use the wizard-created strings shown in the matrix below instead. For MNP specifically: only a B2B2C Port-In goes to approval — a Consumer/HRN Port-In (the evidenced UJ-069 case) still lands in status "Pending" as before, since that reflects a real port request awaiting the donor operator, not a B2B2C order awaiting manager sign-off. Also: CUST-1002 (HRN) will trigger the advance-payment gate on the New Postpaid wizard, which independently sets the order to Submitted for Approval regardless of the B2B2C checkbox.</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
@@ -17,7 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bell Notifications" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bulk Notes" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leads (Sales)" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Codes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Postpaid Plans &amp; Discounts" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Codes" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -493,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -637,10 +638,22 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Postpaid Plans &amp; Discounts</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>The RED plan tiers and eligible discounts shown on the New Postpaid Activation wizard's redesigned Plan &amp; Add-ons step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>Verification Codes</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>The demo password and OTP/verification code used everywhere a code is required (password reset, MFA, change password).</t>
         </is>
@@ -792,6 +805,383 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Postpaid Plans &amp; Discounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>public/mock-data/products.json + addons-discounts.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Redesigned "Plan &amp; Add-ons" step (New Postpaid Activation wizard only — Fixed Line/FWA/MNP/Pre-to-Post still use the original single-column ProductPlanStep and are unaffected). Plan names follow the evidenced "Postpaid Red &lt;price&gt; Promotion" naming family (Pre-to-Post guided-journey Plan step); the specific data/speed values per tier are representative demo catalogue entries, same as the rest of products.json. Discounts reuse the Loyalty Discount concept/rate already evidenced in addons-discounts.json (ADO-7103) rather than inventing new discount types.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Product ID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Plan Name</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>MRC (QAR)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Voice</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Popular?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>PROD-100</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Postpaid Extra Promotion</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Unlimited local</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>5G Ready</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>PROD-104</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Postpaid Red 350 Promotion</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Unlimited local</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>5G Ready</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>PROD-105</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Postpaid Red 500 Promotion</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Unlimited local</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>5G Ready</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>PROD-106</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Postpaid RED Unlimited Promotion</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>750</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Unlimited local</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>5G Priority</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Eligible Discounts (per plan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Discount ID</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Applies to Product ID</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>ADO-7103</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>PROD-201</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>6 Month Retention Discount</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>15% discount for retained customers</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>ADO-7105</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>PROD-100</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Loyalty Discount</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>15% off for existing Vodafone customers</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>ADO-7106</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>PROD-104</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Loyalty Discount</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>15% off for existing Vodafone customers</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>ADO-7107</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>PROD-105</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Loyalty Discount</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>15% off for existing Vodafone customers</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>ADO-7108</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>PROD-106</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Loyalty Discount</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>15% off for existing Vodafone customers</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
@@ -18,7 +18,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bulk Notes" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leads (Sales)" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Postpaid Plans &amp; Discounts" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Codes" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Number Selection" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Codes" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -650,10 +651,22 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>Number Selection</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Seeded MSISDN inventory plus how to test the Manual MSISDN Entry card's valid/blocked/malformed paths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>Verification Codes</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>The demo password and OTP/verification code used everywhere a code is required (password reset, MFA, change password).</t>
         </is>
@@ -1182,6 +1195,155 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Number Selection</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>public/mock-data/numbers.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>The Number Selection step (New Postpaid/Fixed Line/FWA wizards) also has a "Manual MSISDN Entry" card below the grid for reserving any MSISDN not in the seeded inventory below — type a full +974-prefixed 8-digit number (e.g. +974 3300 9999) and click "Reserve Custom Number". To test its rejection paths: type +97433001003 (seeded as Blocked below) to see the "already blocked" error, or an incomplete/malformed number to see the format error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>MSISDN</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Price (QAR)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Value Tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>+97433001001</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>+97433001002</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Star</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>+97433001003</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
@@ -19,7 +19,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leads (Sales)" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Postpaid Plans &amp; Discounts" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Number Selection" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Codes" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Devices (DOI)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Codes" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -663,10 +664,22 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>Devices (DOI)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>The device catalogue and colour/storage/stock options on the redesigned Device &amp; DOI step, and its DOI declaration gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>Verification Codes</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>The demo password and OTP/verification code used everywhere a code is required (password reset, MFA, change password).</t>
         </is>
@@ -1344,6 +1357,219 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Devices (DOI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>public/mock-data/device-installments.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>New Postpaid Activation's redesigned "Device &amp; DOI" step. DOI = Device on Installment (BR-114/BR-106/BR-329) — the step's own declaration section is correctly labelled "Device on Installment (DOI) Declaration", not "Declaration of Intent". Selecting any device below (not "SIM only") requires ticking both DOI checkboxes before Continue enables — "SIM only" skips the declaration entirely. Total contract value = upfront + (monthly instalment x term); Monthly total = device instalment + the Plan &amp; Add-ons total from the earlier step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Price (QAR)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Default Upfront</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Default Term</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Default Monthly</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Colours</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Stock Status</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Trade-in Bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S24</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Onyx Black, Marble Grey, Cobalt Violet</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>128 GB, 256 GB</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>iPhone 15</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>3800</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>800</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Natural Titanium, Black Titanium</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>128 GB, 256 GB, 512 GB</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Delivery Only</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy Watch 6</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Graphite, Silver</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>16 GB</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
@@ -20,7 +20,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Postpaid Plans &amp; Discounts" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Number Selection" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Devices (DOI)" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Codes" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prepaid Activation Eligibility" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prepaid Full Journey" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Codes" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -676,10 +678,34 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>Prepaid Activation Eligibility</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Which seeded customers pass/fail the New Prepaid Activation wizard's eligibility gate (blacklist + BR-347 line cap) and payment gating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Prepaid Full Journey</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>The full 9-step Prepaid wizard beyond eligibility/payment: plan tiers, discounts, the BR-348 SIM card charge, HRN approval routing, SIM depletion, fulfilment status progression, and notifications.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>Verification Codes</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>The demo password and OTP/verification code used everywhere a code is required (password reset, MFA, change password).</t>
         </is>
@@ -836,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1194,6 +1220,87 @@
       <c r="E20" s="5" t="inlineStr">
         <is>
           <t>15% off for existing Vodafone customers</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>ADO-7109</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>PROD-301</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Prepaid Welcome Discount</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>10% off the starter pack charge for new prepaid activations</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>ADO-7110</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>PROD-302</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Prepaid Welcome Discount</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>10% off the starter pack charge for new prepaid activations</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>ADO-7111</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>PROD-303</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Prepaid Welcome Discount</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>10% off the starter pack charge for new prepaid activations</t>
         </is>
       </c>
     </row>
@@ -1570,6 +1677,426 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Prepaid Activation Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>src/components/domain/EligibilityGateStep.tsx + ruleEngine.ts (BR-347) + customers.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>New Prepaid Activation wizard (SCR-190/191/192) now has 9 steps: Contact -&gt; Eligibility -&gt; Address &amp; Contact Details -&gt; Plan &amp; Discount -&gt; Number Selection -&gt; SIM Type -&gt; Checkout -&gt; CAF &amp; Key Information -&gt; Payment (originally just Contact -&gt; Number -&gt; SIM Serial, with no gate before reservation, no plan/CAF/checkout at all, and no payment before the order was marked Complete — see the "Prepaid Full Journey" sheet for the other 6 steps and full onSubmit mechanics). Eligibility reuses the same EligibilityGateStep component New Postpaid Activation uses, in a "prepaid" mode: it checks blacklist status (same as postpaid) plus a prepaid-specific line -count cap (BR-347 in ruleEngine.ts, sourced from this journey's own BRSD BR-003 — NOT the general catalogue's unrelated BR-003 "Try &amp; Buy 30-Day Waiver"), and it deliberately hides the HRN-advance-payment banner and credit-limit badge that postpaid shows, since MPRA_001_CAM_04/ECC_03/BAM_01 explicitly exclude both from Prepaid Activation. On submit, the wizard finds-or-creates a "Consumer Mobile Prepaid" account for the resolved customer (visible on their Customer 360 &gt; Profile &gt; Accounts list) and increments that customer's activePrepaidLines by 1 — so re-running the wizard against the same customer moves them closer to (or past) their BR-347 cap. That increment only persists for the current browser session; a full page reload re-seeds from these JSON files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Customer ID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ID Type</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Nationality / Segment</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Active postpaid lines</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Active prepaid lines</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Expected Eligibility result</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>CUST-1004</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>QID</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Qatari</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>blacklisted</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Blocked — blacklist check fails regardless of line count (blacklistReason: "Outstanding dues &gt; threshold").</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>CUST-1005</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>GCC ID</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Emirati</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Blocked — GCC ID cap is 2 prepaid lines (BR-003) and this customer is already at 2. Same customer is also pre-seeded at the postpaid BR-288 cap, so it exercises both gates' failure paths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>CUST-1002</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Passport</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Nepalese (HRN)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Passes at 1/2 — a boundary case one below the Passport cap of 2. HRN flag is true on this customer but the HRN banner/credit-limit badge stay hidden per CAM_04, unlike on the postpaid wizard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>CUST-1001</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>QID</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Qatari</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Passes — Qatari nationals are unrestricted under BR-003 regardless of line count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>CUST-1003</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>QID</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Qatari</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Passes — unrestricted, clean baseline customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>CUST-1006</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Diplomatic ID</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Passes — BR-003's source text does not cover Diplomatic ID at all, so it is left unrestricted rather than an invented cap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>CUST-9001</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>QID</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Qatari</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Passes — QA test identity, unrestricted (Qatari).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Prepaid Full Journey</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>src/modules/mobile-prepaid/screens/NewPrepaidWizard.tsx + ruleEngine.ts (BR-348)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Closes the remaining Mobile Prepaid Activation BRSD gaps beyond the P1 fixes above (2026-09-11 follow-up). Full step list: Contact -&gt; Eligibility -&gt; Address &amp; Contact Details (MPRA_001_CAM_05, reuses ZsbAddressStep, non-blocking) -&gt; Plan &amp; Discount (MPRA_001_QPC_01-04, new PrepaidPlanStep) -&gt; Number Selection -&gt; SIM Type (MPRA_001_SIM_01, reuses SimTypeStep — Physical or eSIM only; "Printed eSIM"/"Virtual eSIM" are not modelled as distinct selectable options, matching the same component postpaid uses) -&gt; Checkout (MPRA_001_CVC_01-03, new PrepaidCheckoutStep) -&gt; CAF &amp; Key Information (MPRA_001_CAF_01-03, reuses CafSignatureCapture) -&gt; Payment (MPRA_001_PAY_01/02, reuses WinCashPaymentStep, now gated on the FULL checkout total, not just the number price). On submit: physical SIMs are depleted (stockStatus -&gt; Issued, MPRA_001_PAY_03) — try reusing a serial from a completed order and it now correctly shows "This SIM is already assigned"; HRN customers route to the Order Approval Queue instead of auto-completing (BR-004, new "New Prepaid Activation" approval-matrix entry, same mechanism as postpaid's HRN/B2B2C routing) with orderSubType recording the derived HRN flag (MPRA_001_CAM_03); non-HRN orders run through a ~1 second simulated fulfilment delay before flipping from "Open" to "Complete" (MPRA_001_NET_02-06 — the first place in this app an order progresses through an intermediate status rather than jumping straight to a terminal one); and a real osb-notifications record is created (MPRA_001_NOT_01, visible on Customer 360 &gt; Notifications), not just a toast. Not built, and why: Qnomy queue ticketing (MPRA_001_JSM_01) and a Tracking Record entity (DF-01) have zero implementation anywhere else in this app — building them only for prepaid would be a fabricated one-off, not a real reused capability. Email is captured/displayed but not "verified" (INT-04), consistent with every other journey including postpaid. The BRSD's "notify all active MSISDNs on the QID" recipient list (DF-20) is not modelled — this schema has no cross-line directory to resolve that from, so the notification targets only the just-activated MSISDN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Aspect</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Details / how to test it</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Plan tiers</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>PROD-300 SIM only (QAR 0), PROD-301 Prepaid Red 25, PROD-302 Prepaid Red 50 (POPULAR), PROD-303 Prepaid Red 100 — each with a starter pack charge, data/voice allowance and pack validity instead of postpaid's monthly recurring charge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Discounts</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>ADO-7109/7110/7111 "Prepaid Welcome Discount" (-10%), one per Red tier — MPRA_001_QPC_04's "Special discount."</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>SIM card charge (BR-348/BR-013)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Threshold QAR 10 for QID, QAR 40 for Passport, compared against the selected pack's starter pack charge. Below threshold: a QAR 15 placeholder charge applies (the BRSD names the threshold but never the charge amount itself — flagged in ruleEngine.ts). Try Prepaid Red 25 (QAR 25) with a Passport contact: 25 &lt; 40, so the charge applies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>HRN approval routing test</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>CUST-1002 (Passport, HRN) — any prepaid order for this customer routes to "Submitted for Approval" and appears in Orders &gt; Approval Queue requiring the "Back Office Fulfilment Agent" role, instead of completing automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>SIM depletion test</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Complete one order with a Physical SIM and a specific serial (e.g. the always-available 8974412345678901234), then start a second order and enter the same serial at the SIM Type step — it now correctly shows "This SIM is already assigned."</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Fulfilment status progression test</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Complete a non-HRN order and immediately check Customer 360 &gt; Orders — status briefly reads the intermediate state before settling on "Complete" a moment later (the ~900ms simulated NET_02-06 fulfilment delay).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Notification test</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>After any completed or approval-routed order, open Customer 360 &gt; Notifications for that customer — a new row appears sourced from osb-notifications.json, not just a toast.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2910,7 +3437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2938,7 +3465,7 @@
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>The Approval Queue is EMPTY by default — none of the 5 seeded orders are in "Submitted for Approval" status. To populate it: run the New Postpaid Activation, New Fixed Line, New FWA, or MNP Port-In wizard (Sales workspace) and tick the "B2B2C order" checkbox on the contact step — all four wizards now write an order-type string that matches an approval-matrix category (New Postpaid Activation / New Fixed Line Activation / New FWA Postpaid Outdoor Order / MNP Postpaid Port-In), so the role gate applies to all of them. Note the two seeded historical orders ORD-90003/ORD-90004 use slightly different order-type strings ("New FWA 5G Outdoor Activation" / "New Fixed Line - Triple Play") than the matrix — that is harmless since both are already Complete/Open and never re-enter the approval flow, but do not use those exact strings as a template if you are hand-editing an order into "Submitted for Approval" for testing; use the wizard-created strings shown in the matrix below instead. For MNP specifically: only a B2B2C Port-In goes to approval — a Consumer/HRN Port-In (the evidenced UJ-069 case) still lands in status "Pending" as before, since that reflects a real port request awaiting the donor operator, not a B2B2C order awaiting manager sign-off. Also: CUST-1002 (HRN) will trigger the advance-payment gate on the New Postpaid wizard, which independently sets the order to Submitted for Approval regardless of the B2B2C checkbox.</t>
+          <t>The Approval Queue is EMPTY by default — none of the 5 seeded orders are in "Submitted for Approval" status. To populate it: run the New Postpaid Activation, New Fixed Line, New FWA, or MNP Port-In wizard (Sales workspace) and tick the "B2B2C order" checkbox on the contact step — all four wizards now write an order-type string that matches an approval-matrix category (New Postpaid Activation / New Fixed Line Activation / New FWA Postpaid Outdoor Order / MNP Postpaid Port-In), so the role gate applies to all of them. Note the two seeded historical orders ORD-90003/ORD-90004 use slightly different order-type strings ("New FWA 5G Outdoor Activation" / "New Fixed Line - Triple Play") than the matrix — that is harmless since both are already Complete/Open and never re-enter the approval flow, but do not use those exact strings as a template if you are hand-editing an order into "Submitted for Approval" for testing; use the wizard-created strings shown in the matrix below instead. For MNP specifically: only a B2B2C Port-In goes to approval — a Consumer/HRN Port-In (the evidenced UJ-069 case) still lands in status "Pending" as before, since that reflects a real port request awaiting the donor operator, not a B2B2C order awaiting manager sign-off. Also: CUST-1002 (HRN) will trigger the advance-payment gate on the New Postpaid wizard, which independently sets the order to Submitted for Approval regardless of the B2B2C checkbox. New Prepaid Activation now has its own matrix entry too — any prepaid order for an HRN customer (CUST-1002) routes to approval the same way, no B2B2C checkbox involved (prepaid has no B2B2C concept).</t>
         </is>
       </c>
     </row>
@@ -3208,56 +3735,68 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>New Prepaid Activation</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Back Office Fulfilment Agent</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Reject Reasons</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Reason Code</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Reason Label</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>ID_DOC_MISMATCH</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>ID Document details do not match customer profile</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>ADDRESS_INCOMPLETE</t>
+          <t>ID_DOC_MISMATCH</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Installation address incomplete</t>
+          <t>ID Document details do not match customer profile</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>ADDRESS_INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Installation address incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
           <t>CREDIT_CHECK_FAILED</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Credit check failed</t>
         </is>

--- a/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Seeded tickets for the Support workspace.</t>
+          <t>The full ticket lifecycle (assignment, SLA/RAG, escalation, resolution/closure, reopen, RBAC) and what each seeded ticket demonstrates.</t>
         </is>
       </c>
     </row>
@@ -2249,17 +2249,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2279,7 +2281,7 @@
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Password is the SAME for every Staff ID: Vodafone@123 (placeholder — real VFQ credentials are not confirmed, see D-02/OI-AGN-04). "Resulting agent identity" is who you actually become after login (name/job title/team) — it is looked up from users-agents.json by matching keywords in the persona name, NOT the Staff ID itself, so two Staff IDs can log you in as the same person. VFQ12343 and VFQ12344 both match on the word "Manager" and both resolve to Rachel Thompson — this is a real quirk of the matching logic (src/engines/agentProfileEngine.ts), not a typo here.</t>
+          <t>2026-09-11: Staff ID table replaced with the user-supplied Staff ID/Role/Channel/Context-card mapping — 7 Staff IDs now (was 6); VFQ12347 is new, and every ID from VFQ12342 onward shifted role vs. the previous table. Password is the SAME for every Staff ID: Vodafone@123 (placeholder — real VFQ credentials are not confirmed, see D-02/OI-AGN-04). Channel and Context card are recorded for traceability only — no context-card UI exists yet to consume them (Queue Number + Ticket Number for Retail, CTI Reference only for Back-office/Telephonic, Hidden for Field/System). "Resulting agent identity" is who you actually become after login (name/job title/team) — it is looked up from users-agents.json by matching keywords in the persona name, NOT the Staff ID itself, so multiple Staff IDs can log you in as the same person. VFQ12342, VFQ12344 and VFQ12345 all match on "Manager"/"Approver" and all three resolve to Rachel Thompson — a real quirk of the matching logic (src/engines/agentProfileEngine.ts), not a typo here.</t>
         </is>
       </c>
     </row>
@@ -2301,25 +2303,35 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Context card</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
           <t>Resulting agent name</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Resulting job title</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Resulting team</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>Resulting userId</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>What to test with it</t>
         </is>
@@ -2343,25 +2355,35 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>Retail / in-store</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Queue Number + Ticket Number</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>Fatima Al-Kuwari</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Sales Agent</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Retail Sales</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>USR-1101</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Default frontline agent. Use for: Customer Search, Task View as an agent with assigned tasks, claiming un-role-gated approval items.</t>
         </is>
@@ -2380,32 +2402,42 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Back Office / Fulfilment</t>
+          <t>Retail Store Manager / Approver</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Omar Hassan</t>
+          <t>Retail / in-store</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Back Office Fulfilment Agent</t>
+          <t>Queue Number + Ticket Number</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Order Fulfilment</t>
+          <t>Rachel Thompson</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>USR-1102</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Use for: approving "New Postpaid Activation" B2B2C orders (approval matrix requires this exact role).</t>
+          <t>Sales Management</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>USR-1103</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Use for: approving "MNP Postpaid Port-In" orders (approval matrix requires this exact role); assigning tasks to team members (supervisor-only action).</t>
         </is>
       </c>
     </row>
@@ -2422,32 +2454,42 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Manager / Approver</t>
+          <t>Back Office / Fulfilment</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Rachel Thompson</t>
+          <t>Back-office</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>CTI Reference only</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Sales Management</t>
+          <t>Omar Hassan</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>USR-1103</t>
+          <t>Back Office Fulfilment Agent</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Use for: approving "MNP Postpaid Port-In" orders (approval matrix requires this exact role); assigning tasks to team members (supervisor-only action).</t>
+          <t>Order Fulfilment</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>USR-1102</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Use for: approving "New Postpaid Activation" B2B2C orders (approval matrix requires this exact role).</t>
         </is>
       </c>
     </row>
@@ -2464,32 +2506,42 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Enterprise Account Manager</t>
+          <t>Back Office Manager / Approver</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>Back-office</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>CTI Reference only</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>Rachel Thompson</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Sales Manager</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Sales Management</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>USR-1103</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>Resolves to the SAME identity as VFQ12343 (see note above) — role label shown at login differs, but the signed-in agent is identical.</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Resolves to the SAME identity as VFQ12342/12345 (see note above) — role label shown at login differs, but the signed-in agent is identical.</t>
         </is>
       </c>
     </row>
@@ -2506,32 +2558,42 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Field Technician</t>
+          <t>Enterprise Account Manager</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Fatima Al-Kuwari</t>
+          <t>Telephonic / back-office</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Sales Agent</t>
+          <t>CTI Reference only</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Retail Sales</t>
+          <t>Rachel Thompson</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>USR-1101</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Falls back to the default agent — no seeded field-technician identity exists in users-agents.json.</t>
+          <t>Sales Management</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>USR-1103</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Resolves to the SAME identity as VFQ12342/12344 (see note above).</t>
         </is>
       </c>
     </row>
@@ -2548,114 +2610,196 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>IT Operations</t>
+          <t>Field Technician</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>Field (no queue, no CTI)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Hidden</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>Fatima Al-Kuwari</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Sales Agent</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Retail Sales</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>USR-1101</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>Falls back to the default agent — no seeded IT-ops identity exists in users-agents.json.</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Falls back to the default agent — no seeded field-technician identity exists in users-agents.json.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>anything else</t>
+          <t>VFQ12347</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>any value</t>
+          <t>Vodafone@123</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>IT Operations</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>System / no customer interaction</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hidden</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fatima Al-Kuwari</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sales Agent</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Login is rejected with "Staff ID not recognised." — only the 6 Staff IDs above are recognised.</t>
+          <t>Retail Sales</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>USR-1101</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Falls back to the default agent — no seeded IT-ops identity exists in users-agents.json.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
+          <t>anything else</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>any value</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Login is rejected with "Staff ID not recognised." — only the 7 Staff IDs above are recognised.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
           <t>any of the above</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>wrong password</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Login is rejected with "Incorrect password." — use this to test the login failure state.</t>
         </is>
@@ -3846,7 +3990,7 @@
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Tasks with no assigned agent (blank below) are visible to every logged-in agent. Tasks assigned to a specific userId are ONLY visible to that agent — log in as USR-1101 (Fatima, Staff ID VFQ12341) vs USR-1102 (Omar, VFQ12342) to see the difference (ATV-02 per-agent scoping). Log in as VFQ12343/12344 (Rachel, Sales Manager) to test assigning an unassigned task to a team member — that control only appears for the Manager persona.</t>
+          <t>Tasks with no assigned agent (blank below) are visible to every logged-in agent. Tasks assigned to a specific userId are ONLY visible to that agent — log in as USR-1101 (Fatima, Staff ID VFQ12341) vs USR-1102 (Omar, VFQ12343) to see the difference (ATV-02 per-agent scoping). Log in as VFQ12342/12344/12345 (Rachel, Sales Manager) to test assigning an unassigned task to a team member — that control only appears for the Manager persona.</t>
         </is>
       </c>
     </row>
@@ -4218,16 +4362,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4240,14 +4386,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>public/mock-data/trouble-tickets.json</t>
+          <t>public/mock-data/trouble-tickets.json + TicketDetail.tsx</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Support workspace — open TT-40001 for CUST-1001 to test an open ticket, TT-40002 for a resolved one.</t>
+          <t>2026-09-11 rebuild closes most of the gaps found in the Trouble Ticket BRSD forensic gap analysis: assignment (Assign to me / supervisor Reassign queue), SLA/RAG (BR-349, computed live against slaDueAt) with auto-escalation, manual escalation with mandatory reason, resolution (Resolution Code + Hashtag gate, RES-01) -&gt; Complete (gated on no open activities, RES-08) -&gt; Close (closes all activities, triggers a CSA-01/02 notification) -&gt; Reopen (mandatory reason + a 7-day window, P-12 placeholder) or Cancel (mandatory reason code), real Activities (manual + auto-logged), Attachments (metadata only, blocked on Closed/Cancelled per ATT-03), and an Audit Trail tab wired to audit-trail.json. Status vocabulary was corrected to match the BRSD's own terms (Not Solved/Assigned/Escalate/Solved/Completed/Closed/Cancelled) — "Open"/"Reopened" never appear in the source and were replaced. RBAC (§12 of the gap report): Resolution is gated to the Complaints Team/Supervisor/Admin personas — switch role via the profile menu's "Switch role" select to "Complaints Team (Mobile and Fixed)" to test it; the default Retail/Sales Agent persona sees "Resolution requires Complaints Team — use Escalate to route it" instead. The Audit Trail tab is hidden for the Retail/Sales Agent and FL Agents personas (BR-067) and visible for every other persona.</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4420,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Area</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -4285,6 +4431,16 @@
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Queue</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Assigned To</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>SLA Target (h)</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4457,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Not Solved</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -4311,18 +4467,26 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Slow Data Performance</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>3-Medium</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
           <t>FL Agents</t>
         </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
@@ -4338,7 +4502,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -4348,17 +4512,239 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>IPTV Channel Issue</t>
+          <t>IPTV</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>4-Low</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Complaints Team</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Current Agent</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TT-40003</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>CUST-1002</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Escalate</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Mobile Complaints</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>2-High</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Complaints Team</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Current Agent</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TT-40004</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>CUST-1004</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Human Error Complaints</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Agent Error</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>3-Medium</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Complaints Team</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Current Agent</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TT-40005</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>CUST-2001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>SOC</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Provisioning</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>1-ASAP</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Complaints Team</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Current Agent</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>What each seeded ticket demonstrates</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>What it tests</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>TT-40001</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Fresh, unassigned, SLA Green — the baseline ticket for Assign/Escalate/Resolve/Complete/Close/Reopen testing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>TT-40002</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Closed 3 days before the demo date — within the 7-day reopen window, so Reopen should succeed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>TT-40003</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>HRN customer (48h Expatriate SLA target), created far enough in the past that its SLA is already breached — a real RAG-Red, auto-escalated ("Escalate" status) demo ticket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>TT-40004</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Closed well over 7 days before the demo date — outside the reopen window, so Reopen is disabled with the RES-10 guidance message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TT-40005</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise customer (CUST-2001) — demonstrates CRE-16 priority derivation locking to 1-ASAP instead of a freely-chosen value; also a duplicate-detection hit when creating a new SOC ticket for the same customer.</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/parithimalsaravanan/claude-projects/vfq/vfq-dxp-app/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4795B1F2-9AF3-F94B-94B9-7BE5417B2B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92ACBFF3-6A36-BE4F-B905-DCD3808E2C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="2300" windowWidth="38400" windowHeight="23400" firstSheet="4" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -1570,21 +1570,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1593,17 +1584,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1910,26 +1940,26 @@
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26" style="4" customWidth="1"/>
-    <col min="2" max="2" width="95" style="4" customWidth="1"/>
-    <col min="3" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="1" width="26" style="2" customWidth="1"/>
+    <col min="2" max="2" width="95" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1940,122 +1970,122 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="4" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2076,91 +2106,91 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" style="4" customWidth="1"/>
-    <col min="2" max="2" width="18" style="4" customWidth="1"/>
-    <col min="3" max="4" width="20" style="4" customWidth="1"/>
-    <col min="5" max="5" width="18" style="4" customWidth="1"/>
-    <col min="6" max="6" width="16" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="1" width="14" style="15" customWidth="1"/>
+    <col min="2" max="2" width="18" style="15" customWidth="1"/>
+    <col min="3" max="4" width="20" style="15" customWidth="1"/>
+    <col min="5" max="5" width="18" style="15" customWidth="1"/>
+    <col min="6" max="6" width="16" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="13" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="14" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="14" t="s">
         <v>342</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="14" t="s">
         <v>343</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="14" t="s">
         <v>345</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="14" t="s">
         <v>346</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="14" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2181,310 +2211,310 @@
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" style="4" customWidth="1"/>
-    <col min="2" max="2" width="18" style="4" customWidth="1"/>
-    <col min="3" max="3" width="20" style="4" customWidth="1"/>
-    <col min="4" max="4" width="10" style="4" customWidth="1"/>
-    <col min="5" max="5" width="44" style="4" customWidth="1"/>
-    <col min="6" max="6" width="16" style="4" customWidth="1"/>
-    <col min="7" max="7" width="12" style="4" customWidth="1"/>
-    <col min="8" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="1" width="14" style="15" customWidth="1"/>
+    <col min="2" max="2" width="18" style="15" customWidth="1"/>
+    <col min="3" max="3" width="20" style="15" customWidth="1"/>
+    <col min="4" max="4" width="10" style="15" customWidth="1"/>
+    <col min="5" max="5" width="44" style="15" customWidth="1"/>
+    <col min="6" max="6" width="16" style="15" customWidth="1"/>
+    <col min="7" max="7" width="12" style="15" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="18" t="s">
         <v>347</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="6" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="13" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="14" t="s">
         <v>355</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="14" t="s">
         <v>356</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="14">
         <v>250</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="14">
         <v>30</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="14" t="s">
         <v>357</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="G7" s="7"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>360</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="14">
         <v>350</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="14">
         <v>100</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="14" t="s">
         <v>357</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="14" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="14">
         <v>500</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="14">
         <v>250</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="14" t="s">
         <v>357</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="G9" s="7"/>
+      <c r="G9" s="14"/>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="14">
         <v>750</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="14" t="s">
         <v>357</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="G10" s="7"/>
+      <c r="G10" s="14"/>
     </row>
     <row r="13" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="20" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="13" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="14" t="s">
         <v>372</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="14" t="s">
         <v>373</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="14" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="14" t="s">
         <v>377</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="14" t="s">
         <v>355</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="14" t="s">
         <v>378</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="14" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="14" t="s">
         <v>380</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="14" t="s">
         <v>378</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="14" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="14" t="s">
         <v>381</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="14" t="s">
         <v>378</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="14" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="14" t="s">
         <v>378</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="14" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="14" t="s">
         <v>383</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="14" t="s">
         <v>384</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="14" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="14" t="s">
         <v>388</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="14" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="14" t="s">
         <v>387</v>
       </c>
     </row>
@@ -2506,107 +2536,107 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18" style="4" customWidth="1"/>
-    <col min="2" max="2" width="12" style="4" customWidth="1"/>
-    <col min="3" max="5" width="14" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="1" width="18" style="15" customWidth="1"/>
+    <col min="2" max="2" width="12" style="15" customWidth="1"/>
+    <col min="3" max="5" width="14" style="15" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="13" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="14" t="s">
         <v>398</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="14" t="s">
         <v>399</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="14">
         <v>0</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="14" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>401</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="14">
         <v>500</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="14" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="14" t="s">
         <v>398</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="14">
         <v>0</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="14" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2628,160 +2658,160 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22" style="4" customWidth="1"/>
-    <col min="2" max="2" width="12" style="4" customWidth="1"/>
-    <col min="3" max="3" width="14" style="4" customWidth="1"/>
-    <col min="4" max="4" width="12" style="4" customWidth="1"/>
-    <col min="5" max="5" width="14" style="4" customWidth="1"/>
-    <col min="6" max="6" width="30" style="4" customWidth="1"/>
-    <col min="7" max="7" width="20" style="4" customWidth="1"/>
-    <col min="8" max="9" width="14" style="4" customWidth="1"/>
-    <col min="10" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="1" width="22" style="15" customWidth="1"/>
+    <col min="2" max="2" width="12" style="15" customWidth="1"/>
+    <col min="3" max="3" width="14" style="15" customWidth="1"/>
+    <col min="4" max="4" width="12" style="15" customWidth="1"/>
+    <col min="5" max="5" width="14" style="15" customWidth="1"/>
+    <col min="6" max="6" width="30" style="15" customWidth="1"/>
+    <col min="7" max="7" width="20" style="15" customWidth="1"/>
+    <col min="8" max="9" width="14" style="15" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="18" t="s">
         <v>406</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="19" t="s">
         <v>407</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="6" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="13" t="s">
         <v>409</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="13" t="s">
         <v>410</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="13" t="s">
         <v>411</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="13" t="s">
         <v>413</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="13" t="s">
         <v>414</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="13" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="14" t="s">
         <v>416</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="14">
         <v>3200</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="14">
         <v>500</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="14">
         <v>12</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="14">
         <v>225</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="14" t="s">
         <v>417</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="14">
         <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="14" t="s">
         <v>420</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="14">
         <v>3800</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="14">
         <v>800</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="14">
         <v>24</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="14">
         <v>125</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="14" t="s">
         <v>421</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="14" t="s">
         <v>422</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="14" t="s">
         <v>423</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="14" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="14">
         <v>1200</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="14">
         <v>200</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="14">
         <v>6</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="14">
         <v>167</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="14" t="s">
         <v>426</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="14" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2803,201 +2833,201 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" style="4" customWidth="1"/>
-    <col min="2" max="2" width="16" style="4" customWidth="1"/>
-    <col min="3" max="3" width="22" style="4" customWidth="1"/>
-    <col min="4" max="5" width="16" style="4" customWidth="1"/>
-    <col min="6" max="6" width="70" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="1" width="14" style="15" customWidth="1"/>
+    <col min="2" max="2" width="16" style="15" customWidth="1"/>
+    <col min="3" max="3" width="22" style="15" customWidth="1"/>
+    <col min="4" max="5" width="16" style="15" customWidth="1"/>
+    <col min="6" max="6" width="70" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="18" t="s">
         <v>427</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="19" t="s">
         <v>428</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="13" t="s">
         <v>429</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="13" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="14" t="s">
         <v>433</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="14" t="s">
         <v>434</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="14" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="14" t="s">
         <v>436</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="14">
         <v>2</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="14">
         <v>2</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="14" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="14" t="s">
         <v>438</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="14">
         <v>1</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="14">
         <v>1</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="14" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="14" t="s">
         <v>433</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="14">
         <v>1</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="14">
         <v>0</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="14" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="14" t="s">
         <v>433</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="14">
         <v>0</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="14">
         <v>0</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="14" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="14" t="s">
         <v>442</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="14">
         <v>0</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="14">
         <v>0</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="14" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="14" t="s">
         <v>433</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="14">
         <v>0</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="14">
         <v>0</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="14" t="s">
         <v>444</v>
       </c>
     </row>
@@ -3019,102 +3049,102 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30" style="4" customWidth="1"/>
-    <col min="2" max="2" width="90" style="4" customWidth="1"/>
-    <col min="3" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="1" width="30" style="15" customWidth="1"/>
+    <col min="2" max="2" width="90" style="15" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="13" t="s">
         <v>447</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="14" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="14" t="s">
         <v>451</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="14" t="s">
         <v>453</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="14" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="14" t="s">
         <v>455</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="14" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="14" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="14" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="14" t="s">
         <v>461</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="14" t="s">
         <v>462</v>
       </c>
     </row>
@@ -3136,105 +3166,105 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="42" style="4" customWidth="1"/>
-    <col min="2" max="2" width="40" style="4" customWidth="1"/>
-    <col min="3" max="3" width="55" style="4" customWidth="1"/>
-    <col min="4" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="1" width="42" style="15" customWidth="1"/>
+    <col min="2" max="2" width="40" style="15" customWidth="1"/>
+    <col min="3" max="3" width="55" style="15" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>465</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="13" t="s">
         <v>466</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>467</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="13" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="14" t="s">
         <v>468</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="14" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="14" t="s">
         <v>470</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>471</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="14" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="14" t="s">
         <v>473</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="14" t="s">
         <v>471</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="14" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="14" t="s">
         <v>475</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="14" t="s">
         <v>471</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="14" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="14" t="s">
         <v>477</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="14" t="s">
         <v>479</v>
       </c>
     </row>
@@ -3256,366 +3286,366 @@
   <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16" style="4" customWidth="1"/>
-    <col min="2" max="2" width="14" style="4" customWidth="1"/>
-    <col min="3" max="3" width="26" style="4" customWidth="1"/>
-    <col min="4" max="4" width="22" style="4" customWidth="1"/>
-    <col min="5" max="5" width="20" style="4" customWidth="1"/>
-    <col min="6" max="6" width="18" style="4" customWidth="1"/>
-    <col min="7" max="7" width="24" style="4" customWidth="1"/>
-    <col min="8" max="8" width="18" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="60" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="1" width="16" style="15" customWidth="1"/>
+    <col min="2" max="2" width="14" style="15" customWidth="1"/>
+    <col min="3" max="3" width="26" style="15" customWidth="1"/>
+    <col min="4" max="4" width="22" style="15" customWidth="1"/>
+    <col min="5" max="5" width="20" style="15" customWidth="1"/>
+    <col min="6" max="6" width="18" style="15" customWidth="1"/>
+    <col min="7" max="7" width="24" style="15" customWidth="1"/>
+    <col min="8" max="8" width="18" style="15" customWidth="1"/>
+    <col min="9" max="9" width="16" style="15" customWidth="1"/>
+    <col min="10" max="10" width="60" style="15" customWidth="1"/>
+    <col min="11" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="6" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="13" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="14" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="14" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="14" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="14" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="14" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="14" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="14" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="14" t="s">
         <v>94</v>
       </c>
     </row>
@@ -3637,333 +3667,333 @@
   <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" style="4" customWidth="1"/>
-    <col min="2" max="2" width="20" style="4" customWidth="1"/>
-    <col min="3" max="3" width="12" style="4" customWidth="1"/>
-    <col min="4" max="4" width="24" style="4" customWidth="1"/>
-    <col min="5" max="5" width="16" style="4" customWidth="1"/>
-    <col min="6" max="6" width="30" style="4" customWidth="1"/>
-    <col min="7" max="7" width="18" style="4" customWidth="1"/>
-    <col min="8" max="9" width="14" style="4" customWidth="1"/>
-    <col min="10" max="10" width="60" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="1" width="14" style="15" customWidth="1"/>
+    <col min="2" max="2" width="20" style="15" customWidth="1"/>
+    <col min="3" max="3" width="12" style="10" customWidth="1"/>
+    <col min="4" max="4" width="24" style="15" customWidth="1"/>
+    <col min="5" max="5" width="16" style="15" customWidth="1"/>
+    <col min="6" max="6" width="30" style="15" customWidth="1"/>
+    <col min="7" max="7" width="18" style="15" customWidth="1"/>
+    <col min="8" max="9" width="14" style="10" customWidth="1"/>
+    <col min="10" max="10" width="60" style="15" customWidth="1"/>
+    <col min="11" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="6" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="13" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="14" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="14" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="14" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="14" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="14" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="14" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="14" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3974,6 +4004,7 @@
     <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="8" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Public</oddFooter>
   </headerFooter>
@@ -3985,161 +4016,161 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="14" style="4" customWidth="1"/>
-    <col min="3" max="3" width="30" style="4" customWidth="1"/>
-    <col min="4" max="4" width="12" style="4" customWidth="1"/>
-    <col min="5" max="5" width="18" style="4" customWidth="1"/>
-    <col min="6" max="6" width="34" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="2" width="14" style="15" customWidth="1"/>
+    <col min="3" max="3" width="30" style="15" customWidth="1"/>
+    <col min="4" max="4" width="12" style="15" customWidth="1"/>
+    <col min="5" max="5" width="18" style="15" customWidth="1"/>
+    <col min="6" max="6" width="34" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="13" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="14" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="14" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="14" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="14" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="14" t="s">
         <v>90</v>
       </c>
     </row>
@@ -4161,256 +4192,256 @@
   <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22" style="4" customWidth="1"/>
-    <col min="2" max="2" width="44" style="4" customWidth="1"/>
-    <col min="3" max="4" width="14" style="4" customWidth="1"/>
-    <col min="5" max="5" width="20" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="1" width="22" style="15" customWidth="1"/>
+    <col min="2" max="2" width="44" style="15" customWidth="1"/>
+    <col min="3" max="4" width="14" style="15" customWidth="1"/>
+    <col min="5" max="5" width="20" style="15" customWidth="1"/>
+    <col min="6" max="6" width="14" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="13" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="14" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="14" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="14" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="14" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="14" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="20" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="21" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="13" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="14" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="14" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="14" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="14" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="14" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="20" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="13" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="14" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="14" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="14" t="s">
         <v>225</v>
       </c>
     </row>
@@ -4432,261 +4463,261 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" style="4" customWidth="1"/>
-    <col min="2" max="2" width="34" style="4" customWidth="1"/>
-    <col min="3" max="4" width="14" style="4" customWidth="1"/>
-    <col min="5" max="5" width="12" style="4" customWidth="1"/>
-    <col min="6" max="6" width="34" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="1" width="14" style="15" customWidth="1"/>
+    <col min="2" max="2" width="34" style="15" customWidth="1"/>
+    <col min="3" max="4" width="14" style="15" customWidth="1"/>
+    <col min="5" max="5" width="12" style="15" customWidth="1"/>
+    <col min="6" max="6" width="34" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="13" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="14" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="14" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="14" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="14" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="14" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="14" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="14" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="14" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="14" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="14" t="s">
         <v>54</v>
       </c>
     </row>
@@ -4708,272 +4739,272 @@
   <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" style="4" customWidth="1"/>
-    <col min="2" max="2" width="90" style="4" customWidth="1"/>
-    <col min="3" max="3" width="14" style="4" customWidth="1"/>
-    <col min="4" max="4" width="20" style="4" customWidth="1"/>
-    <col min="5" max="5" width="14" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12" style="4" customWidth="1"/>
-    <col min="7" max="7" width="18" style="4" customWidth="1"/>
-    <col min="8" max="8" width="16" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14" style="4" customWidth="1"/>
-    <col min="10" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="1" width="14" style="15" customWidth="1"/>
+    <col min="2" max="2" width="90" style="15" customWidth="1"/>
+    <col min="3" max="3" width="14" style="15" customWidth="1"/>
+    <col min="4" max="4" width="20" style="15" customWidth="1"/>
+    <col min="5" max="5" width="14" style="15" customWidth="1"/>
+    <col min="6" max="6" width="12" style="15" customWidth="1"/>
+    <col min="7" max="7" width="18" style="15" customWidth="1"/>
+    <col min="8" max="8" width="16" style="15" customWidth="1"/>
+    <col min="9" max="9" width="14" style="15" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="18" t="s">
         <v>260</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="6" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="13" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="14">
         <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="14">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="14">
         <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="14">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="14">
         <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="20" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="13" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="14" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="14" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="14" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="14" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="14" t="s">
         <v>299</v>
       </c>
     </row>
@@ -4995,126 +5026,126 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16" style="4" customWidth="1"/>
-    <col min="2" max="2" width="14" style="4" customWidth="1"/>
-    <col min="3" max="3" width="12" style="4" customWidth="1"/>
-    <col min="4" max="4" width="26" style="4" customWidth="1"/>
-    <col min="5" max="5" width="55" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="1" width="16" style="15" customWidth="1"/>
+    <col min="2" max="2" width="14" style="15" customWidth="1"/>
+    <col min="3" max="3" width="12" style="15" customWidth="1"/>
+    <col min="4" max="4" width="26" style="15" customWidth="1"/>
+    <col min="5" max="5" width="55" style="15" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="13" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="14" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="14" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="14" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="14" t="s">
         <v>317</v>
       </c>
     </row>
@@ -5136,82 +5167,82 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" style="4" customWidth="1"/>
-    <col min="2" max="2" width="30" style="4" customWidth="1"/>
-    <col min="3" max="3" width="22" style="4" customWidth="1"/>
-    <col min="4" max="4" width="60" style="4" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="1" width="14" style="15" customWidth="1"/>
+    <col min="2" max="2" width="30" style="15" customWidth="1"/>
+    <col min="3" max="3" width="22" style="15" customWidth="1"/>
+    <col min="4" max="4" width="60" style="15" customWidth="1"/>
+    <col min="5" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="13" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="14" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="14" t="s">
         <v>330</v>
       </c>
     </row>

--- a/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/parithimalsaravanan/claude-projects/vfq/vfq-dxp-app/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1245D963-2386-EB40-8981-D6A54C078120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE90C55-6906-3144-9B04-627C2F7C9491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="499">
   <si>
     <t>Customer Search</t>
   </si>
@@ -86,9 +86,6 @@
     <t>Ahmed Al-Sulaiti</t>
   </si>
   <si>
-    <t>+97455512001</t>
-  </si>
-  <si>
     <t>ahmed.alsulaiti@example.qa</t>
   </si>
   <si>
@@ -113,9 +110,6 @@
     <t>Bimal Thapa</t>
   </si>
   <si>
-    <t>+97455512002</t>
-  </si>
-  <si>
     <t>bimal.thapa@example.com</t>
   </si>
   <si>
@@ -134,9 +128,6 @@
     <t>Fatima Al-Kuwari</t>
   </si>
   <si>
-    <t>+97455512003</t>
-  </si>
-  <si>
     <t>fatima.alkuwari@example.qa</t>
   </si>
   <si>
@@ -149,9 +140,6 @@
     <t>Mohammed Al-Emadi</t>
   </si>
   <si>
-    <t>+97455512004</t>
-  </si>
-  <si>
     <t>mohammed.alemadi@example.qa</t>
   </si>
   <si>
@@ -164,9 +152,6 @@
     <t>Layla Hassan (Employer Contact)</t>
   </si>
   <si>
-    <t>+97455512005</t>
-  </si>
-  <si>
     <t>layla.hassan@acmeqatar.com</t>
   </si>
   <si>
@@ -185,9 +170,6 @@
     <t>Khalid Al-Mazrouei</t>
   </si>
   <si>
-    <t>+97455512006</t>
-  </si>
-  <si>
     <t>khalid.almazrouei@example.ae</t>
   </si>
   <si>
@@ -206,9 +188,6 @@
     <t>Sophie Laurent</t>
   </si>
   <si>
-    <t>+97455512007</t>
-  </si>
-  <si>
     <t>sophie.laurent@embassy.example</t>
   </si>
   <si>
@@ -222,9 +201,6 @@
   </si>
   <si>
     <t>QA Test User</t>
-  </si>
-  <si>
-    <t>+97450009001</t>
   </si>
   <si>
     <t>qa.test@example.qa</t>
@@ -1705,7 +1681,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1791,6 +1767,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2105,7 +2084,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -2113,7 +2092,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -2121,18 +2100,18 @@
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -2140,111 +2119,111 @@
         <v>0</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2274,7 +2253,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="19" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -2284,7 +2263,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -2294,7 +2273,7 @@
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -2304,44 +2283,44 @@
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -2373,7 +2352,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -2383,7 +2362,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -2393,62 +2372,62 @@
     </row>
     <row r="4" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>7</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2481,7 +2460,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -2491,7 +2470,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -2501,7 +2480,7 @@
     </row>
     <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -2511,33 +2490,33 @@
     </row>
     <row r="6" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C7" s="9">
         <v>250</v>
@@ -2546,19 +2525,19 @@
         <v>30</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="C8" s="9">
         <v>350</v>
@@ -2567,21 +2546,21 @@
         <v>100</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C9" s="9">
         <v>500</v>
@@ -2590,190 +2569,190 @@
         <v>250</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C10" s="9">
         <v>750</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="G10" s="9"/>
     </row>
     <row r="13" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -2803,7 +2782,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="19" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -2813,7 +2792,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -2823,7 +2802,7 @@
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -2833,70 +2812,70 @@
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D7" s="9">
         <v>0</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="D8" s="9">
         <v>500</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="D9" s="9">
         <v>0</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2931,7 +2910,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -2941,7 +2920,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -2951,7 +2930,7 @@
     </row>
     <row r="4" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -2961,36 +2940,36 @@
     </row>
     <row r="6" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="B7" s="9">
         <v>3200</v>
@@ -3005,13 +2984,13 @@
         <v>225</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="I7" s="9">
         <v>300</v>
@@ -3019,7 +2998,7 @@
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="B8" s="9">
         <v>3800</v>
@@ -3034,21 +3013,21 @@
         <v>125</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="B9" s="9">
         <v>1200</v>
@@ -3063,16 +3042,16 @@
         <v>167</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -3104,7 +3083,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -3114,7 +3093,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -3124,7 +3103,7 @@
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -3140,47 +3119,47 @@
         <v>5</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="D8" s="9">
         <v>2</v>
@@ -3189,18 +3168,18 @@
         <v>2</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="D9" s="9">
         <v>1</v>
@@ -3209,7 +3188,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -3220,7 +3199,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="D10" s="9">
         <v>1</v>
@@ -3229,18 +3208,18 @@
         <v>0</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="D11" s="9">
         <v>0</v>
@@ -3249,18 +3228,18 @@
         <v>0</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
@@ -3269,18 +3248,18 @@
         <v>0</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="D13" s="9">
         <v>0</v>
@@ -3289,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -3318,7 +3297,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="19" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="22"/>
@@ -3328,7 +3307,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="22"/>
@@ -3338,7 +3317,7 @@
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="22"/>
@@ -3348,66 +3327,66 @@
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -3437,7 +3416,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="19" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -3447,7 +3426,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -3457,7 +3436,7 @@
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -3467,10 +3446,10 @@
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>12</v>
@@ -3478,57 +3457,57 @@
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -3565,7 +3544,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -3575,7 +3554,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -3585,7 +3564,7 @@
     </row>
     <row r="4" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -3595,322 +3574,322 @@
     </row>
     <row r="6" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="J6" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>110</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="G8" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>122</v>
-      </c>
       <c r="H8" s="9" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>126</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E10" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="J10" s="9" t="s">
         <v>129</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -4019,60 +3998,60 @@
       <c r="D7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="30">
+        <v>97455512001</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="H7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="I7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="30">
+        <v>97455512002</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="G8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="H8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="J8" s="9" t="s">
         <v>27</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B9" s="9">
         <v>27798765432</v>
@@ -4081,30 +4060,30 @@
         <v>14</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="30">
+        <v>97455512003</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>31</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B10" s="9">
         <v>29011122233</v>
@@ -4113,30 +4092,30 @@
         <v>14</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>37</v>
+        <v>33</v>
+      </c>
+      <c r="E10" s="30">
+        <v>97455512004</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="J10" s="9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B11" s="9">
         <v>28855544433</v>
@@ -4145,121 +4124,121 @@
         <v>14</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>42</v>
+        <v>37</v>
+      </c>
+      <c r="E11" s="30">
+        <v>97455512005</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B12" s="13">
         <v>784202312345678</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>49</v>
+        <v>43</v>
+      </c>
+      <c r="E12" s="30">
+        <v>97455512006</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="I12" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>56</v>
+        <v>49</v>
+      </c>
+      <c r="E13" s="30">
+        <v>97455512007</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="I13" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>62</v>
+        <v>54</v>
+      </c>
+      <c r="E14" s="30">
+        <v>97450009001</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="G14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="I14" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -4289,7 +4268,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="28" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -4300,7 +4279,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -4311,7 +4290,7 @@
     </row>
     <row r="4" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="29" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="B4" s="27"/>
       <c r="C4" s="27"/>
@@ -4322,22 +4301,22 @@
     </row>
     <row r="6" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>3</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="G6" s="14" t="s">
         <v>12</v>
@@ -4345,10 +4324,10 @@
     </row>
     <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="15" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>15</v>
@@ -4357,174 +4336,174 @@
         <v>13</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="G9" s="15" t="s">
         <v>483</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>490</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>492</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>24</v>
-      </c>
       <c r="D10" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>
@@ -4554,7 +4533,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -4564,7 +4543,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -4574,7 +4553,7 @@
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -4584,122 +4563,122 @@
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>167</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -4731,7 +4710,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -4741,7 +4720,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -4751,7 +4730,7 @@
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -4761,19 +4740,19 @@
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>3</v>
@@ -4781,19 +4760,19 @@
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>13</v>
@@ -4801,177 +4780,177 @@
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -5003,7 +4982,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -5013,7 +4992,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -5023,7 +5002,7 @@
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -5033,222 +5012,222 @@
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -5284,7 +5263,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -5294,7 +5273,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -5304,7 +5283,7 @@
     </row>
     <row r="4" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -5314,57 +5293,57 @@
     </row>
     <row r="6" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I7" s="9">
         <v>24</v>
@@ -5372,28 +5351,28 @@
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="I8" s="9">
         <v>24</v>
@@ -5401,28 +5380,28 @@
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>274</v>
-      </c>
       <c r="H9" s="9" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="I9" s="9">
         <v>48</v>
@@ -5430,28 +5409,28 @@
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="I10" s="9">
         <v>24</v>
@@ -5459,28 +5438,28 @@
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="I11" s="9">
         <v>24</v>
@@ -5488,55 +5467,55 @@
     </row>
     <row r="14" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -5568,7 +5547,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="19" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -5578,7 +5557,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -5588,7 +5567,7 @@
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -5598,87 +5577,87 @@
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>

--- a/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/parithimalsaravanan/claude-projects/vfq/vfq-dxp-app/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE90C55-6906-3144-9B04-627C2F7C9491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE94B60-11BD-054A-A9E1-3EECAD795E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -1681,7 +1681,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1770,6 +1770,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3899,6 +3905,7 @@
     <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="8" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;"Aptos"&amp;10 &amp;K000000_x000D_# Public</oddFooter>
   </headerFooter>
@@ -3943,12 +3950,12 @@
       <c r="E2" s="17"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="4" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
+    <row r="4" spans="1:10" ht="83" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="31" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="17"/>
-      <c r="C4" s="18"/>
+      <c r="C4" s="32"/>
       <c r="D4" s="17"/>
       <c r="E4" s="17"/>
       <c r="F4" s="17"/>

--- a/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE94B60-11BD-054A-A9E1-3EECAD795E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="23400" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -1681,7 +1681,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1729,10 +1729,25 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1741,22 +1756,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1768,14 +1771,8 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2089,20 +2086,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2258,34 +2255,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="24" t="s">
         <v>74</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
       <c r="D1" s="17"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="22" t="s">
         <v>305</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="31" t="s">
         <v>306</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
@@ -2357,7 +2354,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>318</v>
       </c>
       <c r="B1" s="17"/>
@@ -2367,7 +2364,7 @@
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="16" t="s">
         <v>319</v>
       </c>
       <c r="B2" s="17"/>
@@ -2465,7 +2462,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>78</v>
       </c>
       <c r="B1" s="17"/>
@@ -2475,7 +2472,7 @@
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="16" t="s">
         <v>334</v>
       </c>
       <c r="B2" s="17"/>
@@ -2485,7 +2482,7 @@
       <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="19" t="s">
         <v>335</v>
       </c>
       <c r="B4" s="17"/>
@@ -2787,34 +2784,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="24" t="s">
         <v>80</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
       <c r="D1" s="17"/>
       <c r="E1" s="17"/>
-      <c r="F1" s="22"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="22" t="s">
         <v>379</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
       <c r="E2" s="17"/>
-      <c r="F2" s="22"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="31" t="s">
         <v>380</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
       <c r="E4" s="17"/>
-      <c r="F4" s="22"/>
+      <c r="F4" s="21"/>
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
@@ -2915,7 +2912,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>82</v>
       </c>
       <c r="B1" s="17"/>
@@ -2925,7 +2922,7 @@
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="16" t="s">
         <v>393</v>
       </c>
       <c r="B2" s="17"/>
@@ -2935,7 +2932,7 @@
       <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="19" t="s">
         <v>394</v>
       </c>
       <c r="B4" s="17"/>
@@ -3088,7 +3085,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>84</v>
       </c>
       <c r="B1" s="17"/>
@@ -3098,7 +3095,7 @@
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="16" t="s">
         <v>414</v>
       </c>
       <c r="B2" s="17"/>
@@ -3108,7 +3105,7 @@
       <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="19" t="s">
         <v>415</v>
       </c>
       <c r="B4" s="17"/>
@@ -3302,34 +3299,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="24" t="s">
         <v>86</v>
       </c>
       <c r="B1" s="17"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="22" t="s">
         <v>432</v>
       </c>
       <c r="B2" s="17"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="31" t="s">
         <v>433</v>
       </c>
       <c r="B4" s="17"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
@@ -3421,34 +3418,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="24" t="s">
         <v>450</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="22" t="s">
         <v>451</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="31" t="s">
         <v>452</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
@@ -3549,7 +3546,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>61</v>
       </c>
       <c r="B1" s="17"/>
@@ -3559,7 +3556,7 @@
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="16" t="s">
         <v>90</v>
       </c>
       <c r="B2" s="17"/>
@@ -3569,7 +3566,7 @@
       <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="19" t="s">
         <v>91</v>
       </c>
       <c r="B4" s="17"/>
@@ -3931,31 +3928,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="17"/>
-      <c r="C1" s="18"/>
+      <c r="C1" s="23"/>
       <c r="D1" s="17"/>
       <c r="E1" s="17"/>
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
+      <c r="C2" s="23"/>
       <c r="D2" s="17"/>
       <c r="E2" s="17"/>
       <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:10" ht="83" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="25" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="17"/>
-      <c r="C4" s="32"/>
+      <c r="C4" s="26"/>
       <c r="D4" s="17"/>
       <c r="E4" s="17"/>
       <c r="F4" s="17"/>
@@ -4005,7 +4002,7 @@
       <c r="D7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="9">
         <v>97455512001</v>
       </c>
       <c r="F7" s="9" t="s">
@@ -4037,7 +4034,7 @@
       <c r="D8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="9">
         <v>97455512002</v>
       </c>
       <c r="F8" s="9" t="s">
@@ -4069,7 +4066,7 @@
       <c r="D9" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="9">
         <v>97455512003</v>
       </c>
       <c r="F9" s="9" t="s">
@@ -4101,7 +4098,7 @@
       <c r="D10" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="9">
         <v>97455512004</v>
       </c>
       <c r="F10" s="9" t="s">
@@ -4133,7 +4130,7 @@
       <c r="D11" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="9">
         <v>97455512005</v>
       </c>
       <c r="F11" s="9" t="s">
@@ -4165,7 +4162,7 @@
       <c r="D12" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="9">
         <v>97455512006</v>
       </c>
       <c r="F12" s="9" t="s">
@@ -4197,7 +4194,7 @@
       <c r="D13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="9">
         <v>97455512007</v>
       </c>
       <c r="F13" s="9" t="s">
@@ -4229,7 +4226,7 @@
       <c r="D14" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="9">
         <v>97450009001</v>
       </c>
       <c r="F14" s="9" t="s">
@@ -4274,37 +4271,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>467</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="27" t="s">
         <v>468</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="4" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="30" t="s">
         <v>469</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
     </row>
     <row r="6" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
@@ -4539,7 +4536,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>64</v>
       </c>
       <c r="B1" s="17"/>
@@ -4549,7 +4546,7 @@
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="16" t="s">
         <v>150</v>
       </c>
       <c r="B2" s="17"/>
@@ -4559,7 +4556,7 @@
       <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="19" t="s">
         <v>151</v>
       </c>
       <c r="B4" s="17"/>
@@ -4716,7 +4713,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>66</v>
       </c>
       <c r="B1" s="17"/>
@@ -4726,7 +4723,7 @@
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="16" t="s">
         <v>174</v>
       </c>
       <c r="B2" s="17"/>
@@ -4736,7 +4733,7 @@
       <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="19" t="s">
         <v>175</v>
       </c>
       <c r="B4" s="17"/>
@@ -4988,7 +4985,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>68</v>
       </c>
       <c r="B1" s="17"/>
@@ -4998,7 +4995,7 @@
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="16" t="s">
         <v>213</v>
       </c>
       <c r="B2" s="17"/>
@@ -5008,7 +5005,7 @@
       <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="19" t="s">
         <v>214</v>
       </c>
       <c r="B4" s="17"/>
@@ -5269,7 +5266,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>70</v>
       </c>
       <c r="B1" s="17"/>
@@ -5279,7 +5276,7 @@
       <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="16" t="s">
         <v>247</v>
       </c>
       <c r="B2" s="17"/>
@@ -5289,7 +5286,7 @@
       <c r="F2" s="17"/>
     </row>
     <row r="4" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="19" t="s">
         <v>248</v>
       </c>
       <c r="B4" s="17"/>
@@ -5553,34 +5550,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="24" t="s">
         <v>72</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
       <c r="D1" s="17"/>
       <c r="E1" s="17"/>
-      <c r="F1" s="22"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="22" t="s">
         <v>287</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
       <c r="E2" s="17"/>
-      <c r="F2" s="22"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="31" t="s">
         <v>288</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
       <c r="E4" s="17"/>
-      <c r="F4" s="22"/>
+      <c r="F4" s="21"/>
     </row>
     <row r="6" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">

--- a/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/parithimalsaravanan/claude-projects/vfq/vfq-dxp-app/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_02ECEE0795978F7BAC9A6928DA3DFF3A2E271DC3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE414ED-B951-B248-B204-7ACFBF36785B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="23400" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="23400" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -4552,7 +4552,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="43" customWidth="1"/>
-    <col min="2" max="2" width="47.33203125" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="60.5" style="41" customWidth="1"/>
     <col min="3" max="3" width="53.33203125" style="41" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27" style="43" customWidth="1"/>
     <col min="5" max="5" width="25.83203125" style="41" customWidth="1"/>

--- a/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Test_Data_Reference.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/parithimalsaravanan/claude-projects/vfq/vfq-dxp-app/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE414ED-B951-B248-B204-7ACFBF36785B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4A19FF-2544-2A4C-8DB4-DD54C737E200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="23400" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="20400" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
-    <sheet name="Persona" sheetId="2" r:id="rId2"/>
+    <sheet name="Persona (Original)" sheetId="2" r:id="rId2"/>
     <sheet name="Persona by Approach" sheetId="3" r:id="rId3"/>
     <sheet name="Login Credentials" sheetId="4" r:id="rId4"/>
     <sheet name="Customer Search" sheetId="5" r:id="rId5"/>
@@ -35,9 +35,23 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Customer Search'!$A$1:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'ID Lookup (MOI Fetch)'!$A$1:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Persona by Approach'!$A$1:$F$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -4552,7 +4566,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="43" customWidth="1"/>
-    <col min="2" max="2" width="60.5" style="41" customWidth="1"/>
+    <col min="2" max="2" width="47.33203125" style="41" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="53.33203125" style="41" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27" style="43" customWidth="1"/>
     <col min="5" max="5" width="25.83203125" style="41" customWidth="1"/>
@@ -6403,71 +6417,71 @@
     </row>
     <row r="2" spans="1:7" ht="45" customHeight="1">
       <c r="A2" s="25" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>375</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="45" customHeight="1">
       <c r="A3" s="25" t="s">
-        <v>372</v>
+        <v>326</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>377</v>
+        <v>325</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>353</v>
+        <v>324</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" customHeight="1">
       <c r="A4" s="25" t="s">
-        <v>372</v>
+        <v>333</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>363</v>
+        <v>388</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>362</v>
+        <v>332</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="G4" s="25" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" customHeight="1">
@@ -6518,74 +6532,79 @@
     </row>
     <row r="7" spans="1:7" ht="45" customHeight="1">
       <c r="A7" s="25" t="s">
-        <v>333</v>
+        <v>372</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" customHeight="1">
       <c r="A8" s="25" t="s">
-        <v>326</v>
+        <v>372</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>325</v>
+        <v>377</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" customHeight="1">
       <c r="A9" s="25" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>396</v>
+        <v>363</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="F9" s="26" t="s">
         <v>375</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G9" xr:uid="{00000000-0001-0000-0500-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G9">
+      <sortCondition ref="A1:A9"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="8" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
